--- a/reports/pdf_change_20260824.xlsx
+++ b/reports/pdf_change_20260824.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억   ·   현금 43억(1.0%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -791,7 +791,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억   ·   현금 19억(0.5%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -813,644 +813,770 @@
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="20" t="n"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억   ·   현금 1억(0.2%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 6종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 37억(1.5%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 28억(1.3%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>1447078000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>3.95%→4.46%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>421→497</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-222</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-1484309760</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>1.51%→0.80%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>475→253</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 6종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>108162100</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>2.78%→3.14%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>307→348</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>-81607200</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>0.90%→0.62%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>77→53</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>노바렉스</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>26497920</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>0.29%→0.38%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>101→133</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>-60295200</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>7.33%→7.12%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>745→724</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>21725660</v>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>2.98%→3.05%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>680→697</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>-56832000</v>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>1.47%→1.28%</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>121→105</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>58363800</v>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>0.20%→0.40%</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>11→22</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>42698000</v>
+        <v>108162100</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.99%→3.13%</t>
+          <t>2.78%→3.14%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="17" t="n"/>
+          <t>307→348</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-81607200</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>0.90%→0.62%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>77→53</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>26497920</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>0.29%→0.38%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>101→133</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-60295200</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>7.33%→7.12%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>745→724</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>21725660</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2.98%→3.05%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>680→697</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-56832000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>1.47%→1.28%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>121→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>58363800</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>0.20%→0.40%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>11→22</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>42698000</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2.99%→3.13%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
           <t>보로노이  (신규)</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B30" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C30" s="11" t="n">
         <v>25530000</v>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>0.00%→0.09%</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>0→2</t>
         </is>
       </c>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억   ·   현금 3억(0.6%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>프로티나  (신규)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B35" s="11" t="n">
         <v>227</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C35" s="11" t="n">
         <v>991377100</v>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.85%</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>0→227</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>에이프릴바이오</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H35" s="15" t="n">
         <v>-230</v>
       </c>
-      <c r="I31" s="15" t="n">
+      <c r="I35" s="15" t="n">
         <v>-543020800</v>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>2.62%→1.03%</t>
         </is>
       </c>
-      <c r="K31" s="13" t="inlineStr">
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>464→234</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B36" s="11" t="n">
         <v>223</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C36" s="11" t="n">
         <v>418488490</v>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>1.99%→3.07%</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>655→878</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>리브스메드</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n">
+      <c r="H36" s="15" t="n">
         <v>-116</v>
       </c>
-      <c r="I32" s="15" t="n">
+      <c r="I36" s="15" t="n">
         <v>-461743800</v>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>2.87%→1.73%</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>349→233</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>알지노믹스</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B37" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C37" s="11" t="n">
         <v>265500900</v>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>3.38%→3.83%</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>498→572</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>한스바이오메드</t>
         </is>
       </c>
-      <c r="H33" s="15" t="n">
+      <c r="H37" s="15" t="n">
         <v>-91</v>
       </c>
-      <c r="I33" s="15" t="n">
+      <c r="I37" s="15" t="n">
         <v>-184201290</v>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>1.65%→1.17%</t>
         </is>
       </c>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>402→311</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>에스티팜</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B38" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C38" s="11" t="n">
         <v>261014600</v>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>5.47%→6.15%</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>256→278</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>휴젤</t>
         </is>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H38" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I34" s="15" t="n">
+      <c r="I38" s="15" t="n">
         <v>-583100000</v>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>3.56%→2.56%</t>
         </is>
       </c>
-      <c r="K34" s="13" t="inlineStr">
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="20" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="20" t="n"/>
-      <c r="G36" s="20" t="n"/>
-      <c r="H36" s="20" t="n"/>
-      <c r="I36" s="20" t="n"/>
-      <c r="J36" s="20" t="n"/>
-      <c r="K36" s="20" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="19">
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260824.xlsx
+++ b/reports/pdf_change_20260824.xlsx
@@ -815,7 +815,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 37억(1.5%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -839,7 +839,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 28억(1.3%)      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>

--- a/reports/pdf_change_20260824.xlsx
+++ b/reports/pdf_change_20260824.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>47</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2184160500</v>
+        <v>2171498700</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-14</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-407893500</v>
+        <v>-405528900</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>-13</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-883993500</v>
+        <v>-878868900</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>-11</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-856152000</v>
+        <v>-851188800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>-4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-414000000</v>
+        <v>-411600000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -815,7 +815,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -839,7 +839,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -935,7 +935,7 @@
         <v>76</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1447078000</v>
+        <v>1438490000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>-222</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1484309760</v>
+        <v>-1475500800</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 6종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 6종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1068,11 +1068,11 @@
         <v>41</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>108162100</v>
+        <v>97391400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.78%→3.14%</t>
+          <t>2.73%→3.09%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1089,11 +1089,11 @@
         <v>-24</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-81607200</v>
+        <v>-84626400</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.62%</t>
+          <t>1.02%→0.70%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
@@ -1112,11 +1112,11 @@
         <v>32</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>26497920</v>
+        <v>25527040</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.38%</t>
+          <t>0.30%→0.40%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1133,11 +1133,11 @@
         <v>-21</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-60295200</v>
+        <v>-56332500</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>7.33%→7.12%</t>
+          <t>7.49%→7.27%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -1156,11 +1156,11 @@
         <v>17</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>21725660</v>
+        <v>20631200</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>2.98%→3.05%</t>
+          <t>3.09%→3.17%</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1177,11 +1177,11 @@
         <v>-16</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-56832000</v>
+        <v>-53161600</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>1.47%→1.28%</t>
+          <t>1.51%→1.31%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1200,11 +1200,11 @@
         <v>11</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>58363800</v>
+        <v>50468000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.40%</t>
+          <t>0.19%→0.38%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1228,11 +1228,11 @@
         <v>5</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>42698000</v>
+        <v>39775000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2.99%→3.13%</t>
+          <t>3.04%→3.19%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1256,11 +1256,11 @@
         <v>2</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>25530000</v>
+        <v>22510800</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.09%</t>
+          <t>0.00%→0.08%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억      당일 2026-08-24  vs  전영업일 2026-08-21      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1373,7 +1373,7 @@
         <v>227</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>991377100</v>
+        <v>974715300</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>-230</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-543020800</v>
+        <v>-533894400</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>223</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>418488490</v>
+        <v>411455070</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>-116</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-461743800</v>
+        <v>-453983400</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>74</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>265500900</v>
+        <v>261038700</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>-91</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-184201290</v>
+        <v>-181105470</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>22</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>261014600</v>
+        <v>256627800</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>-20</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-583100000</v>
+        <v>-573300000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
